--- a/excel-files/NAVOTAS/ANGELES NATIONAL HIGH SCHOOL.xlsx
+++ b/excel-files/NAVOTAS/ANGELES NATIONAL HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DF800B8-D5C0-B24F-8053-41F64E75AA3D}"/>
+  <xr:revisionPtr revIDLastSave="208" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BF9148E-2942-45BD-B431-64AA336B9B02}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -229,6 +229,9 @@
     <t>MAPEH</t>
   </si>
   <si>
+    <t>RO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quantity based on Target ADM-SLM - Q1 </t>
   </si>
   <si>
@@ -312,15 +315,12 @@
   <si>
     <t>Arts</t>
   </si>
-  <si>
-    <t>RO</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1832,6 +1832,13 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1855,13 +1862,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -2940,6 +2940,13 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2976,13 +2983,6 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3025,7 +3025,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="61" tableBorderDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3042,7 +3042,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
@@ -3098,7 +3098,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
   <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
@@ -3471,17 +3471,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.0859375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.84375" customWidth="1"/>
-    <col min="3" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.1015625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.19921875" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="29.25" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="21" customHeight="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="25.5" customHeight="1">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="20.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3607,12 +3607,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="24" customHeight="1">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="20.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3712,12 +3712,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -3737,7 +3737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="27" customHeight="1">
       <c r="A16" s="1">
         <v>3</v>
       </c>
@@ -3777,7 +3777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="21" customHeight="1">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="20.25">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3847,7 +3847,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="24" customHeight="1">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="20.25">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="27" customHeight="1">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="33.75" customHeight="1">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="33.75" customHeight="1">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="33.75" customHeight="1">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="27.75" customHeight="1">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="27.75" customHeight="1">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4037,7 +4037,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1">
       <c r="A32" s="1">
         <v>5</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1">
       <c r="A34" s="1">
         <v>5</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="39" customHeight="1">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="27.75" customHeight="1">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4157,7 +4157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="27.75" customHeight="1">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="27.75" customHeight="1">
       <c r="A38" s="1">
         <v>5</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="27.75" customHeight="1">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" ht="27.75" customHeight="1">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4227,7 +4227,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1">
       <c r="A41" s="1">
         <v>6</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1">
       <c r="A42" s="1">
         <v>6</v>
       </c>
@@ -4267,7 +4267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1">
       <c r="A43" s="1">
         <v>6</v>
       </c>
@@ -4287,7 +4287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1">
       <c r="A44" s="1">
         <v>6</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="36.75" customHeight="1">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="27.75" customHeight="1">
       <c r="A46" s="1">
         <v>6</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" ht="27.75" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -4417,7 +4417,7 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="27.75" customHeight="1">
       <c r="A51" s="10">
         <v>7</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="27.75" customHeight="1">
       <c r="A52" s="10">
         <v>7</v>
       </c>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="27.75" customHeight="1">
       <c r="A53" s="10">
         <v>7</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="27.75" customHeight="1">
       <c r="A54" s="10">
         <v>7</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="39" customHeight="1">
       <c r="A55" s="10">
         <v>7</v>
       </c>
@@ -4541,7 +4541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="27.75" customHeight="1">
       <c r="A56" s="10">
         <v>7</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="27.75" customHeight="1">
       <c r="A57" s="10">
         <v>7</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="27.75" customHeight="1">
       <c r="A58" s="10">
         <v>7</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="27.75" customHeight="1">
       <c r="A59" s="10">
         <v>7</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" ht="27.75" customHeight="1">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -4663,7 +4663,7 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="27.75" customHeight="1">
       <c r="A61" s="10">
         <v>8</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="27.75" customHeight="1">
       <c r="A62" s="10">
         <v>8</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="27.75" customHeight="1">
       <c r="A63" s="10">
         <v>8</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="27.75" customHeight="1">
       <c r="A64" s="10">
         <v>8</v>
       </c>
@@ -4759,7 +4759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="27.75" customHeight="1">
       <c r="A65" s="10">
         <v>8</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="27.75" customHeight="1">
       <c r="A66" s="10">
         <v>8</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="27.75" customHeight="1">
       <c r="A67" s="10">
         <v>8</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="27.75" customHeight="1">
       <c r="A68" s="10">
         <v>8</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="27.75" customHeight="1">
       <c r="A69" s="10">
         <v>8</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" ht="27.75" customHeight="1">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -4869,7 +4869,7 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="27.75" customHeight="1">
       <c r="A71" s="10">
         <v>9</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="27.75" customHeight="1">
       <c r="A72" s="10">
         <v>9</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="27.75" customHeight="1">
       <c r="A73" s="10">
         <v>9</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="27.75" customHeight="1">
       <c r="A74" s="10">
         <v>9</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="27.75" customHeight="1">
       <c r="A75" s="10">
         <v>9</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="27.75" customHeight="1">
       <c r="A76" s="10">
         <v>9</v>
       </c>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="27.75" customHeight="1">
       <c r="A77" s="10">
         <v>9</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ht="27.75" customHeight="1">
       <c r="A78" s="10">
         <v>9</v>
       </c>
@@ -5029,7 +5029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="27.75" customHeight="1">
       <c r="A79" s="10">
         <v>9</v>
       </c>
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" ht="27.75" customHeight="1">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -5059,7 +5059,7 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="27.75" customHeight="1">
       <c r="A81" s="10">
         <v>10</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="27.75" customHeight="1">
       <c r="A82" s="10">
         <v>10</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="27.75" customHeight="1">
       <c r="A83" s="10">
         <v>10</v>
       </c>
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="27.75" customHeight="1">
       <c r="A84" s="10">
         <v>10</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="27.75" customHeight="1">
       <c r="A85" s="10">
         <v>10</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="27.75" customHeight="1">
       <c r="A86" s="10">
         <v>10</v>
       </c>
@@ -5179,7 +5179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="27.75" customHeight="1">
       <c r="A87" s="10">
         <v>10</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="27.75" customHeight="1">
       <c r="A88" s="10">
         <v>10</v>
       </c>
@@ -5219,7 +5219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="27.75" customHeight="1">
       <c r="A89" s="10">
         <v>10</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" ht="27.75" customHeight="1">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -5249,7 +5249,7 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" ht="39.75" customHeight="1">
       <c r="A91" s="1" t="s">
         <v>24</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ht="27.75" customHeight="1">
       <c r="A92" s="1" t="s">
         <v>24</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="27.75" customHeight="1">
       <c r="A93" s="1" t="s">
         <v>24</v>
       </c>
@@ -5309,7 +5309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="27.75" customHeight="1">
       <c r="A94" s="1" t="s">
         <v>24</v>
       </c>
@@ -5329,7 +5329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="40.5" customHeight="1">
       <c r="A95" s="1" t="s">
         <v>24</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="38.25" customHeight="1">
       <c r="A96" s="1" t="s">
         <v>24</v>
       </c>
@@ -5369,7 +5369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" ht="27.75" customHeight="1">
       <c r="A97" s="1" t="s">
         <v>24</v>
       </c>
@@ -5389,7 +5389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="47.25" customHeight="1">
       <c r="A98" s="1" t="s">
         <v>24</v>
       </c>
@@ -5415,12 +5415,15 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E91:E98 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E51:E59" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F91:F98 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F51:F59" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{F7D7B578-631D-4667-81BF-E7747A147386}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5432,36 +5435,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AA127"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.4140625" customWidth="1"/>
-    <col min="2" max="2" width="27.84375" customWidth="1"/>
-    <col min="3" max="3" width="17.08203125" customWidth="1"/>
-    <col min="4" max="4" width="26.09765625" customWidth="1"/>
-    <col min="5" max="5" width="23.13671875" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5625" customWidth="1"/>
-    <col min="8" max="9" width="20.84765625" customWidth="1"/>
-    <col min="10" max="10" width="13.71875" customWidth="1"/>
-    <col min="11" max="11" width="35.51171875" customWidth="1"/>
-    <col min="12" max="12" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.609375" customWidth="1"/>
-    <col min="14" max="15" width="20.84765625" customWidth="1"/>
-    <col min="16" max="16" width="21.5234375" customWidth="1"/>
-    <col min="17" max="17" width="33.359375" customWidth="1"/>
-    <col min="18" max="18" width="25.828125" customWidth="1"/>
-    <col min="19" max="19" width="32.8203125" customWidth="1"/>
-    <col min="20" max="21" width="20.84765625" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="35.5703125" customWidth="1"/>
+    <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.5703125" customWidth="1"/>
+    <col min="14" max="15" width="20.85546875" customWidth="1"/>
+    <col min="16" max="16" width="21.5703125" customWidth="1"/>
+    <col min="17" max="17" width="33.42578125" customWidth="1"/>
+    <col min="18" max="18" width="25.85546875" customWidth="1"/>
+    <col min="19" max="19" width="32.85546875" customWidth="1"/>
+    <col min="20" max="21" width="20.85546875" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25.01953125" customWidth="1"/>
-    <col min="24" max="24" width="15.33203125" customWidth="1"/>
-    <col min="25" max="25" width="20.84765625" customWidth="1"/>
-    <col min="26" max="26" width="14.796875" customWidth="1"/>
-    <col min="27" max="27" width="15.19921875" customWidth="1"/>
+    <col min="23" max="23" width="25" customWidth="1"/>
+    <col min="24" max="24" width="15.28515625" customWidth="1"/>
+    <col min="25" max="25" width="20.85546875" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="D1" s="42" t="s">
         <v>33</v>
       </c>
@@ -5495,7 +5498,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -5578,7 +5581,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="30.6" customHeight="1">
       <c r="A3" s="39" t="s">
         <v>61</v>
       </c>
@@ -5645,7 +5648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -5657,7 +5660,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="34.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5726,7 +5729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="20.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5795,7 +5798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="20.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5864,7 +5867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="20.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5933,7 +5936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="20.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6002,7 +6005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="20.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6071,7 +6074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="20.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6140,7 +6143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="20.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6209,7 +6212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6222,7 +6225,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="34.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6291,7 +6294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="20.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6360,7 +6363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="20.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6429,7 +6432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="20.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6498,7 +6501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="20.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6567,7 +6570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="20.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6636,7 +6639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="20.25">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6705,7 +6708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="20.25">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6774,7 +6777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6788,7 +6791,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="34.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6857,7 +6860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="20.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -6926,7 +6929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="20.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -6995,7 +6998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="20.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7064,7 +7067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="20.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7133,7 +7136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="20.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7202,7 +7205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="20.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7271,7 +7274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="20.25">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7340,7 +7343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="20.25">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7409,7 +7412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7423,7 +7426,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="20.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7492,7 +7495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="20.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7561,7 +7564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="20.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7630,7 +7633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="20.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7699,7 +7702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="20.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7768,7 +7771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="20.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7837,7 +7840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="20.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -7906,7 +7909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="20.25">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -7975,7 +7978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="20.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8044,7 +8047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8058,7 +8061,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="20.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8127,7 +8130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="20.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8196,7 +8199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="20.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8265,7 +8268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="20.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8334,7 +8337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="20.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8403,7 +8406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="20.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8472,7 +8475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="20.25">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8541,7 +8544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="20.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8610,7 +8613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="20.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8679,7 +8682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8693,7 +8696,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="20.25">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8762,7 +8765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="20.25">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8831,7 +8834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="20.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -8900,7 +8903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="20.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -8969,7 +8972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="20.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9038,7 +9041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="20.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9107,7 +9110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="20.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9176,7 +9179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="20.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9245,7 +9248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="20.25">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9314,7 +9317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9328,7 +9331,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="20.25">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9397,7 +9400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="20.25">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9466,7 +9469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="20.25">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9535,7 +9538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="20.25">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9604,7 +9607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="20.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9673,7 +9676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="20.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9742,7 +9745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="20.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9811,7 +9814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="20.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9880,7 +9883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="20.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -9949,7 +9952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -9963,7 +9966,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="20.25">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -9984,7 +9987,7 @@
         <v>2025</v>
       </c>
       <c r="G73" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="2"/>
@@ -10040,7 +10043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="20.25">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10061,7 +10064,7 @@
         <v>2025</v>
       </c>
       <c r="G74" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H74" s="12">
         <f t="shared" si="2"/>
@@ -10117,7 +10120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="20.25">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10138,7 +10141,7 @@
         <v>2025</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H75" s="12">
         <f t="shared" si="2"/>
@@ -10194,7 +10197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="20.25">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10215,7 +10218,7 @@
         <v>2025</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H76" s="12">
         <f t="shared" si="2"/>
@@ -10271,7 +10274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="20.25">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10292,7 +10295,7 @@
         <v>2025</v>
       </c>
       <c r="G77" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H77" s="12">
         <f t="shared" si="2"/>
@@ -10348,7 +10351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" ht="20.25">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10369,7 +10372,7 @@
         <v>2025</v>
       </c>
       <c r="G78" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H78" s="12">
         <f t="shared" ref="H78:H127" si="22">IF((D78-E78)&lt;0,0,(D78-E78))</f>
@@ -10425,7 +10428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" ht="20.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10446,7 +10449,7 @@
         <v>2025</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H79" s="12">
         <f t="shared" si="22"/>
@@ -10502,7 +10505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="20.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10523,7 +10526,7 @@
         <v>2025</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H80" s="12">
         <f t="shared" si="22"/>
@@ -10579,7 +10582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="20.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10600,7 +10603,7 @@
         <v>2025</v>
       </c>
       <c r="G81" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H81" s="12">
         <f t="shared" si="22"/>
@@ -10656,7 +10659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10670,7 +10673,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="20.25">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10739,7 +10742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="20.25">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10808,7 +10811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="20.25">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10877,7 +10880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="20.25">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10946,7 +10949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="20.25">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -11015,7 +11018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="20.25">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11084,7 +11087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="20.25">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11153,7 +11156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" ht="20.25">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11222,7 +11225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" ht="20.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11291,7 +11294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11305,7 +11308,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="20.25">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11374,7 +11377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="20.25">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11443,7 +11446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="20.25">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11512,7 +11515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" ht="20.25">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11581,7 +11584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="20.25">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11650,7 +11653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="20.25">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11719,7 +11722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="20.25">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11788,7 +11791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="20.25">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11857,7 +11860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="20.25">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -11926,7 +11929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -11940,7 +11943,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" ht="34.5">
       <c r="A103" s="1" t="s">
         <v>24</v>
       </c>
@@ -12009,7 +12012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="20.25">
       <c r="A104" s="1" t="s">
         <v>24</v>
       </c>
@@ -12078,7 +12081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" ht="20.25">
       <c r="A105" s="1" t="s">
         <v>24</v>
       </c>
@@ -12147,7 +12150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="20.25">
       <c r="A106" s="1" t="s">
         <v>24</v>
       </c>
@@ -12216,7 +12219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="34.5">
       <c r="A107" s="1" t="s">
         <v>24</v>
       </c>
@@ -12285,7 +12288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="34.5">
       <c r="A108" s="1" t="s">
         <v>24</v>
       </c>
@@ -12354,7 +12357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" ht="34.5">
       <c r="A109" s="1" t="s">
         <v>24</v>
       </c>
@@ -12423,7 +12426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="34.5">
       <c r="A110" s="1" t="s">
         <v>24</v>
       </c>
@@ -12492,7 +12495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12503,7 +12506,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" ht="20.25">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12565,7 +12568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" ht="20.25">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12627,7 +12630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" ht="20.25">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12689,7 +12692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" ht="20.25">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12751,7 +12754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" ht="20.25">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12813,7 +12816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" ht="20.25">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12875,7 +12878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" ht="20.25">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12937,7 +12940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" ht="20.25">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -12999,7 +13002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" ht="20.25">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13061,7 +13064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" ht="20.25">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13123,7 +13126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" ht="20.25">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13185,7 +13188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" ht="20.25">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13247,7 +13250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" ht="20.25">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13309,7 +13312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" ht="20.25">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13371,7 +13374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" ht="20.25">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13433,7 +13436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" ht="20.25">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13490,186 +13493,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13694,15 +13517,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 X112:X127 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 F73:F81" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G103:G110 G83:G91 G93:G101 G73:G81" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{47BFE8C6-CB23-4AD4-A9B9-90B4ABF26190}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13717,35 +13543,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AB140"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.4140625" customWidth="1"/>
-    <col min="2" max="2" width="31.34375" customWidth="1"/>
-    <col min="3" max="3" width="17.08203125" customWidth="1"/>
-    <col min="4" max="4" width="16.41015625" customWidth="1"/>
-    <col min="5" max="5" width="23.13671875" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5625" customWidth="1"/>
-    <col min="8" max="9" width="20.84765625" customWidth="1"/>
-    <col min="10" max="10" width="13.71875" customWidth="1"/>
-    <col min="11" max="11" width="24.48046875" customWidth="1"/>
-    <col min="12" max="12" width="18.16015625" customWidth="1"/>
-    <col min="13" max="15" width="20.84765625" customWidth="1"/>
-    <col min="16" max="16" width="21.5234375" customWidth="1"/>
-    <col min="17" max="17" width="29.19140625" customWidth="1"/>
-    <col min="18" max="18" width="25.828125" customWidth="1"/>
-    <col min="19" max="19" width="32.8203125" customWidth="1"/>
-    <col min="20" max="21" width="20.84765625" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="24.42578125" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" customWidth="1"/>
+    <col min="13" max="15" width="20.85546875" customWidth="1"/>
+    <col min="16" max="16" width="21.5703125" customWidth="1"/>
+    <col min="17" max="17" width="29.140625" customWidth="1"/>
+    <col min="18" max="18" width="25.85546875" customWidth="1"/>
+    <col min="19" max="19" width="32.85546875" customWidth="1"/>
+    <col min="20" max="21" width="20.85546875" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25.01953125" customWidth="1"/>
-    <col min="24" max="24" width="15.33203125" customWidth="1"/>
-    <col min="25" max="25" width="20.84765625" customWidth="1"/>
-    <col min="26" max="26" width="14.796875" customWidth="1"/>
-    <col min="27" max="27" width="15.19921875" customWidth="1"/>
+    <col min="23" max="23" width="25" customWidth="1"/>
+    <col min="24" max="24" width="15.28515625" customWidth="1"/>
+    <col min="25" max="25" width="20.85546875" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
       <c r="D1" s="42" t="s">
         <v>33</v>
@@ -13780,7 +13606,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -13791,79 +13617,79 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N2" s="40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y2" s="41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z2" s="41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AA2" s="26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="32.25" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -13932,7 +13758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="20.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -14001,7 +13827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="20.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14070,7 +13896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="20.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14139,7 +13965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="20.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14208,7 +14034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="20.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14277,7 +14103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="20.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14346,7 +14172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="20.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14415,8 +14241,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" s="7" customFormat="1"/>
+    <row r="12" spans="1:27" ht="20.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14485,7 +14311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="20.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14554,7 +14380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="20.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14623,7 +14449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="20.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14692,7 +14518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="20.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14761,7 +14587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="20.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14830,7 +14656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="20.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -14899,7 +14725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="20.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14968,8 +14794,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" s="7" customFormat="1"/>
+    <row r="21" spans="1:27" ht="20.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -15038,7 +14864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="20.25">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15107,7 +14933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="20.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15176,7 +15002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="20.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15245,7 +15071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="20.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15314,7 +15140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="20.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15383,7 +15209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="20.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15452,7 +15278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="20.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15521,7 +15347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="20.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15590,8 +15416,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" s="7" customFormat="1"/>
+    <row r="31" spans="1:27" ht="20.25">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15660,7 +15486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="20.25">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15729,7 +15555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="20.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15798,7 +15624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="20.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15867,7 +15693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="20.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15936,7 +15762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="20.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -16005,12 +15831,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="20.25">
       <c r="A37" s="37">
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5">
@@ -16074,12 +15900,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="20.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -16143,7 +15969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="20.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16212,12 +16038,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="20.25">
       <c r="A40" s="37">
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5">
@@ -16281,12 +16107,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="20.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -16350,8 +16176,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" s="7" customFormat="1"/>
+    <row r="43" spans="1:27" ht="20.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16420,7 +16246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="20.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16489,7 +16315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="20.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16558,7 +16384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="20.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16627,7 +16453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="20.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16696,7 +16522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="20.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16765,12 +16591,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="20.25">
       <c r="A49" s="37">
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5">
@@ -16834,12 +16660,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="20.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -16903,7 +16729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="20.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16972,12 +16798,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="20.25">
       <c r="A52" s="37">
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5">
@@ -17041,12 +16867,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="20.25">
       <c r="A53" s="1">
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -17110,8 +16936,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" s="7" customFormat="1"/>
+    <row r="55" spans="1:27" ht="20.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17180,7 +17006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="20.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17249,7 +17075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="20.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17318,7 +17144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="20.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17387,7 +17213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="20.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17456,7 +17282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="20.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17525,12 +17351,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="20.25">
       <c r="A61" s="37">
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5">
@@ -17594,12 +17420,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" ht="20.25">
       <c r="A62" s="1">
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="5">
@@ -17663,7 +17489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="20.25">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17732,12 +17558,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="20.25">
       <c r="A64" s="37">
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5">
@@ -17801,12 +17627,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="20.25">
       <c r="A65" s="1">
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="5">
@@ -17870,8 +17696,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" s="7" customFormat="1"/>
+    <row r="67" spans="1:27" ht="20.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -17940,7 +17766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="20.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -18009,7 +17835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="20.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18078,7 +17904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="20.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18147,7 +17973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="20.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18216,7 +18042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="20.25">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18285,12 +18111,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="20.25">
       <c r="A73" s="38">
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="12">
@@ -18354,12 +18180,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="20.25">
       <c r="A74" s="10">
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -18423,7 +18249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="20.25">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18492,12 +18318,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="20.25">
       <c r="A76" s="38">
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12">
@@ -18561,12 +18387,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="20.25">
       <c r="A77" s="10">
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -18630,8 +18456,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" s="7" customFormat="1"/>
+    <row r="79" spans="1:27" ht="20.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18700,7 +18526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="20.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18769,7 +18595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="20.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18838,7 +18664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" ht="20.25">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18907,7 +18733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="20.25">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18976,7 +18802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="20.25">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19045,12 +18871,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="20.25">
       <c r="A85" s="38">
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="12">
@@ -19114,12 +18940,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="20.25">
       <c r="A86" s="10">
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -19183,7 +19009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="20.25">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19252,12 +19078,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="20.25">
       <c r="A88" s="38">
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C88" s="12"/>
       <c r="D88" s="12">
@@ -19321,12 +19147,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="20.25">
       <c r="A89" s="10">
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -19390,8 +19216,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" s="7" customFormat="1"/>
+    <row r="91" spans="1:27" ht="20.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19460,7 +19286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" ht="20.25">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19481,7 +19307,7 @@
         <v>2025</v>
       </c>
       <c r="G92" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H92" s="12">
         <f t="shared" si="22"/>
@@ -19502,7 +19328,7 @@
         <v>2025</v>
       </c>
       <c r="M92" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="N92" s="12">
         <f t="shared" si="20"/>
@@ -19543,7 +19369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="20.25">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19564,7 +19390,7 @@
         <v>2025</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H93" s="12">
         <f t="shared" si="22"/>
@@ -19585,7 +19411,7 @@
         <v>2025</v>
       </c>
       <c r="M93" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="N93" s="12">
         <f>IF((J93-K93)&lt;0,0,(J93-K93))</f>
@@ -19626,7 +19452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="20.25">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19695,7 +19521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="20.25">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19764,7 +19590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" ht="20.25">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19833,12 +19659,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="20.25">
       <c r="A97" s="38">
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -19902,12 +19728,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="20.25">
       <c r="A98" s="10">
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -19971,7 +19797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="20.25">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -20040,12 +19866,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="20.25">
       <c r="A100" s="38">
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -20109,12 +19935,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="20.25">
       <c r="A101" s="10">
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -20178,8 +20004,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="103" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" s="7" customFormat="1"/>
+    <row r="103" spans="1:27" ht="20.25">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20200,7 +20026,7 @@
         <v>2025</v>
       </c>
       <c r="G103" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H103" s="12">
         <f t="shared" si="22"/>
@@ -20221,7 +20047,7 @@
         <v>2025</v>
       </c>
       <c r="M103" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="N103" s="12">
         <f t="shared" si="20"/>
@@ -20262,7 +20088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="20.25">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20283,7 +20109,7 @@
         <v>2025</v>
       </c>
       <c r="G104" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H104" s="12">
         <f t="shared" si="22"/>
@@ -20339,7 +20165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" ht="20.25">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20375,7 +20201,7 @@
         <v>2025</v>
       </c>
       <c r="M105" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="N105" s="12">
         <f t="shared" si="20"/>
@@ -20416,7 +20242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="20.25">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20485,7 +20311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="20.25">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20554,7 +20380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="20.25">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20623,12 +20449,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" ht="20.25">
       <c r="A109" s="38">
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="12">
@@ -20692,12 +20518,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="20.25">
       <c r="A110" s="10">
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="12">
@@ -20761,7 +20587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" ht="20.25">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20830,12 +20656,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" ht="20.25">
       <c r="A112" s="38">
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="12">
@@ -20899,12 +20725,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:28" ht="20.25">
       <c r="A113" s="10">
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="12">
@@ -20968,8 +20794,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="115" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:28" s="7" customFormat="1"/>
+    <row r="115" spans="1:28" ht="20.25">
       <c r="A115" s="1" t="s">
         <v>24</v>
       </c>
@@ -21038,7 +20864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:28" ht="20.25">
       <c r="A116" s="1" t="s">
         <v>24</v>
       </c>
@@ -21107,7 +20933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:28" ht="20.25">
       <c r="A117" s="1" t="s">
         <v>24</v>
       </c>
@@ -21176,7 +21002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:28" ht="20.25">
       <c r="A118" s="1" t="s">
         <v>24</v>
       </c>
@@ -21245,7 +21071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:28" ht="34.5">
       <c r="A119" s="1" t="s">
         <v>24</v>
       </c>
@@ -21314,7 +21140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:28" ht="20.25">
       <c r="A120" s="1" t="s">
         <v>24</v>
       </c>
@@ -21383,7 +21209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:28" ht="34.5">
       <c r="A121" s="1" t="s">
         <v>24</v>
       </c>
@@ -21452,7 +21278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:28" ht="34.5">
       <c r="A122" s="1" t="s">
         <v>24</v>
       </c>
@@ -21521,8 +21347,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:28" s="7" customFormat="1"/>
+    <row r="124" spans="1:28">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -21552,7 +21378,7 @@
       <c r="AA124" s="7"/>
       <c r="AB124" s="7"/>
     </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:28">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -21582,7 +21408,7 @@
       <c r="AA125" s="7"/>
       <c r="AB125" s="7"/>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:28">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -21612,7 +21438,7 @@
       <c r="AA126" s="7"/>
       <c r="AB126" s="7"/>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:28">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -21642,7 +21468,7 @@
       <c r="AA127" s="7"/>
       <c r="AB127" s="7"/>
     </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:28">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -21672,7 +21498,7 @@
       <c r="AA128" s="7"/>
       <c r="AB128" s="7"/>
     </row>
-    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:28">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -21702,7 +21528,7 @@
       <c r="AA129" s="7"/>
       <c r="AB129" s="7"/>
     </row>
-    <row r="130" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:28">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -21732,7 +21558,7 @@
       <c r="AA130" s="7"/>
       <c r="AB130" s="7"/>
     </row>
-    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:28">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -21762,7 +21588,7 @@
       <c r="AA131" s="7"/>
       <c r="AB131" s="7"/>
     </row>
-    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:28">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -21792,7 +21618,7 @@
       <c r="AA132" s="7"/>
       <c r="AB132" s="7"/>
     </row>
-    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:28">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -21822,7 +21648,7 @@
       <c r="AA133" s="7"/>
       <c r="AB133" s="7"/>
     </row>
-    <row r="134" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:28">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -21852,7 +21678,7 @@
       <c r="AA134" s="7"/>
       <c r="AB134" s="7"/>
     </row>
-    <row r="135" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:28">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -21882,7 +21708,7 @@
       <c r="AA135" s="7"/>
       <c r="AB135" s="7"/>
     </row>
-    <row r="136" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:28">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -21912,7 +21738,7 @@
       <c r="AA136" s="7"/>
       <c r="AB136" s="7"/>
     </row>
-    <row r="137" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:28">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -21942,7 +21768,7 @@
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
     </row>
-    <row r="138" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:28">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -21972,7 +21798,7 @@
       <c r="AA138" s="7"/>
       <c r="AB138" s="7"/>
     </row>
-    <row r="139" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:28">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -22002,7 +21828,7 @@
       <c r="AA139" s="7"/>
       <c r="AB139" s="7"/>
     </row>
-    <row r="140" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:28">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
@@ -22032,186 +21858,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22225,12 +21871,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 M115:M122 Y103:Y113 S103:S113 M103:M113 G103:G113" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025 ,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{7357942B-9C44-4F94-9EF3-22C6B48F3C10}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
